--- a/02_TRAVAIL/Lot7_IK_Avantages/MASTER_FACT_MAN_IK_Avantages.xlsx
+++ b/02_TRAVAIL/Lot7_IK_Avantages/MASTER_FACT_MAN_IK_Avantages.xlsx
@@ -581,6 +581,17 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B2:B501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Valeur non listee. Verifier l'orthographe ou completer le referentiel." promptTitle="Liste" prompt="Associe (REF_Associes)" type="list" errorStyle="warning">
+      <formula1>=PARAMETRES!$A$3:$A$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Valeur non listee. Verifier l'orthographe ou completer le referentiel." promptTitle="Liste" prompt="type_flux_id (REF_Types_Flux Lot 7)" type="list" errorStyle="warning">
+      <formula1>=PARAMETRES!$A$8:$A$14</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Valeur non listee. Verifier l'orthographe ou completer le referentiel." promptTitle="Liste" prompt="mode_paiement_id (REF_Modes_Paiement)" type="list" errorStyle="warning">
+      <formula1>=PARAMETRES!$A$18:$A$22</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
